--- a/feature-th-deidentification/all-profiles.xlsx
+++ b/feature-th-deidentification/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T11:39:33+00:00</t>
+    <t>2026-09-23T11:46:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/all-profiles.xlsx
+++ b/feature-th-deidentification/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T11:46:09+00:00</t>
+    <t>2026-09-23T12:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/all-profiles.xlsx
+++ b/feature-th-deidentification/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T12:15:24+00:00</t>
+    <t>2026-09-23T12:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/all-profiles.xlsx
+++ b/feature-th-deidentification/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T12:19:55+00:00</t>
+    <t>2026-09-23T12:32:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/all-profiles.xlsx
+++ b/feature-th-deidentification/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3181" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3149" uniqueCount="492">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T12:32:00+00:00</t>
+    <t>2026-09-23T18:28:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -410,13 +410,6 @@
   </si>
   <si>
     <t>Hash algorithm (hash only), e.g. 'hmac-sha256'.</t>
-  </si>
-  <si>
-    <t>deidentification-ruleset.rule.propagateTo</t>
-  </si>
-  <si>
-    <t>Reference paths rewritten with the same hash (hash on an id element),
-     e.g. '*.subject', '*.patient'.</t>
   </si>
   <si>
     <t>deidentification-ruleset.rule.maxDays</t>
@@ -1883,7 +1876,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24">
@@ -1891,7 +1884,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25">
@@ -1907,7 +1900,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27">
@@ -1915,7 +1908,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28">
@@ -1969,7 +1962,7 @@
         <v>23</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35">
@@ -1997,7 +1990,7 @@
         <v>29</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39">
@@ -2005,7 +1998,7 @@
         <v>31</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40">
@@ -2013,7 +2006,7 @@
         <v>32</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41">
@@ -2029,7 +2022,7 @@
         <v>36</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2039,7 +2032,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK93"/>
+  <dimension ref="A1:AK92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.15234375" customWidth="true" bestFit="true"/>
@@ -3451,7 +3444,7 @@
         <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>74</v>
@@ -3463,7 +3456,7 @@
         <v>74</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="M14" t="s" s="2">
         <v>127</v>
@@ -3526,7 +3519,7 @@
         <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>74</v>
@@ -3772,7 +3765,7 @@
         <v>74</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>133</v>
@@ -3846,24 +3839,24 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>3</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>74</v>
@@ -3875,13 +3868,13 @@
         <v>74</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -3932,41 +3925,41 @@
         <v>74</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>74</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>74</v>
@@ -3975,18 +3968,20 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="P19" s="2"/>
       <c r="Q19" t="s" s="2">
         <v>74</v>
@@ -4035,30 +4030,30 @@
         <v>74</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>148</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -4069,7 +4064,7 @@
         <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>74</v>
@@ -4081,17 +4076,15 @@
         <v>109</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20" t="s" s="2">
         <v>74</v>
@@ -4140,7 +4133,7 @@
         <v>74</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>75</v>
@@ -4152,18 +4145,18 @@
         <v>74</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>74</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -4180,21 +4173,23 @@
         <v>74</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="K21" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P21" s="2"/>
       <c r="Q21" t="s" s="2">
         <v>74</v>
@@ -4243,7 +4238,7 @@
         <v>74</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>75</v>
@@ -4255,18 +4250,18 @@
         <v>74</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -4283,22 +4278,22 @@
         <v>74</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" t="s" s="2">
@@ -4324,13 +4319,13 @@
         <v>74</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>74</v>
+        <v>170</v>
       </c>
       <c r="AB22" t="s" s="2">
         <v>74</v>
@@ -4348,7 +4343,7 @@
         <v>74</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>75</v>
@@ -4360,22 +4355,22 @@
         <v>74</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
-        <v>74</v>
+        <v>173</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" t="s" s="2">
@@ -4394,16 +4389,16 @@
         <v>74</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="P23" s="2"/>
       <c r="Q23" t="s" s="2">
@@ -4429,13 +4424,13 @@
         <v>74</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>171</v>
+        <v>74</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="AB23" t="s" s="2">
         <v>74</v>
@@ -4453,7 +4448,7 @@
         <v>74</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>75</v>
@@ -4465,22 +4460,22 @@
         <v>74</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" t="s" s="2">
@@ -4499,16 +4494,16 @@
         <v>74</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" t="s" s="2">
@@ -4558,34 +4553,34 @@
         <v>74</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>182</v>
+        <v>74</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" t="s" s="2">
@@ -4604,17 +4599,15 @@
         <v>74</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>183</v>
+        <v>98</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" s="2"/>
       <c r="Q25" t="s" s="2">
         <v>74</v>
@@ -4663,7 +4656,7 @@
         <v>74</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>75</v>
@@ -4675,18 +4668,18 @@
         <v>74</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -4703,7 +4696,7 @@
         <v>74</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>74</v>
@@ -4712,10 +4705,10 @@
         <v>98</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -4783,7 +4776,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>192</v>
@@ -4806,22 +4799,26 @@
         <v>74</v>
       </c>
       <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="K27" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="L27" t="s" s="2">
-        <v>98</v>
+        <v>193</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="P27" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="Q27" t="s" s="2">
         <v>74</v>
       </c>
@@ -4869,7 +4866,7 @@
         <v>74</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>75</v>
@@ -4881,18 +4878,18 @@
         <v>74</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -4915,20 +4912,16 @@
         <v>109</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="P28" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
       <c r="Q28" t="s" s="2">
         <v>74</v>
       </c>
@@ -4976,7 +4969,7 @@
         <v>74</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>75</v>
@@ -4988,18 +4981,18 @@
         <v>74</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -5022,15 +5015,17 @@
         <v>109</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>201</v>
+        <v>86</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P29" s="2"/>
       <c r="Q29" t="s" s="2">
         <v>74</v>
@@ -5079,7 +5074,7 @@
         <v>74</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>75</v>
@@ -5091,22 +5086,22 @@
         <v>74</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>74</v>
+        <v>207</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" t="s" s="2">
@@ -5125,18 +5120,18 @@
         <v>109</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>86</v>
+        <v>208</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="P30" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="Q30" t="s" s="2">
         <v>74</v>
       </c>
@@ -5184,7 +5179,7 @@
         <v>74</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>75</v>
@@ -5196,22 +5191,22 @@
         <v>74</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" t="s" s="2">
@@ -5230,17 +5225,19 @@
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P31" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q31" t="s" s="2">
         <v>74</v>
@@ -5289,7 +5286,7 @@
         <v>74</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>75</v>
@@ -5301,22 +5298,22 @@
         <v>74</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>215</v>
+        <v>74</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" t="s" s="2">
@@ -5335,20 +5332,18 @@
         <v>109</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="P32" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="P32" s="2"/>
       <c r="Q32" t="s" s="2">
         <v>74</v>
       </c>
@@ -5396,7 +5391,7 @@
         <v>74</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>75</v>
@@ -5408,18 +5403,18 @@
         <v>74</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -5427,33 +5422,35 @@
       </c>
       <c r="F33" s="2"/>
       <c r="G33" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>210</v>
+        <v>117</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="P33" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="Q33" t="s" s="2">
         <v>74</v>
       </c>
@@ -5477,13 +5474,13 @@
         <v>74</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>74</v>
+        <v>224</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="AB33" t="s" s="2">
         <v>74</v>
@@ -5501,30 +5498,30 @@
         <v>74</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5550,16 +5547,16 @@
         <v>117</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="P34" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q34" t="s" s="2">
         <v>74</v>
@@ -5587,10 +5584,10 @@
         <v>119</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AB34" t="s" s="2">
         <v>74</v>
@@ -5608,7 +5605,7 @@
         <v>74</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>80</v>
@@ -5620,18 +5617,18 @@
         <v>74</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5648,25 +5645,25 @@
         <v>74</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>117</v>
+        <v>236</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="P35" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q35" t="s" s="2">
         <v>74</v>
@@ -5694,51 +5691,51 @@
         <v>119</v>
       </c>
       <c r="Z35" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG35" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AA35" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -5746,10 +5743,10 @@
       </c>
       <c r="F36" s="2"/>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5758,23 +5755,19 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>238</v>
+        <v>81</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>239</v>
+        <v>93</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="P36" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
       <c r="Q36" t="s" s="2">
         <v>74</v>
       </c>
@@ -5798,13 +5791,13 @@
         <v>74</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>243</v>
+        <v>74</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>244</v>
+        <v>74</v>
       </c>
       <c r="AB36" t="s" s="2">
         <v>74</v>
@@ -5822,41 +5815,41 @@
         <v>74</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>237</v>
+        <v>95</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5868,15 +5861,17 @@
         <v>74</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="P37" s="2"/>
       <c r="Q37" t="s" s="2">
         <v>74</v>
@@ -5913,50 +5908,50 @@
         <v>74</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="AE37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>76</v>
@@ -5968,21 +5963,23 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>98</v>
+        <v>246</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>99</v>
+        <v>247</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>100</v>
+        <v>248</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="P38" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="Q38" t="s" s="2">
         <v>74</v>
       </c>
@@ -6018,19 +6015,19 @@
         <v>74</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="AE38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>105</v>
+        <v>251</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>75</v>
@@ -6042,18 +6039,18 @@
         <v>74</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6061,10 +6058,10 @@
       </c>
       <c r="F39" s="2"/>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -6073,23 +6070,19 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>249</v>
+        <v>93</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="P39" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
       <c r="Q39" t="s" s="2">
         <v>74</v>
       </c>
@@ -6137,41 +6130,41 @@
         <v>74</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>253</v>
+        <v>95</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -6183,15 +6176,17 @@
         <v>74</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="P40" s="2"/>
       <c r="Q40" t="s" s="2">
         <v>74</v>
@@ -6228,53 +6223,53 @@
         <v>74</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="AE40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -6283,21 +6278,23 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>99</v>
+        <v>255</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>100</v>
+        <v>256</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="P41" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="Q41" t="s" s="2">
         <v>74</v>
       </c>
@@ -6333,42 +6330,42 @@
         <v>74</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="AE41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6376,10 +6373,10 @@
       </c>
       <c r="F42" s="2"/>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -6391,20 +6388,18 @@
         <v>109</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="P42" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="P42" s="2"/>
       <c r="Q42" t="s" s="2">
         <v>74</v>
       </c>
@@ -6452,7 +6447,7 @@
         <v>74</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>75</v>
@@ -6464,18 +6459,18 @@
         <v>74</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -6483,10 +6478,10 @@
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -6498,18 +6493,18 @@
         <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="P43" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="Q43" t="s" s="2">
         <v>74</v>
       </c>
@@ -6557,7 +6552,7 @@
         <v>74</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>75</v>
@@ -6569,18 +6564,18 @@
         <v>74</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -6603,17 +6598,17 @@
         <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q44" t="s" s="2">
         <v>74</v>
@@ -6662,7 +6657,7 @@
         <v>74</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>75</v>
@@ -6674,18 +6669,18 @@
         <v>74</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -6693,10 +6688,10 @@
       </c>
       <c r="F45" s="2"/>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>74</v>
@@ -6708,17 +6703,19 @@
         <v>109</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P45" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q45" t="s" s="2">
         <v>74</v>
@@ -6767,7 +6764,7 @@
         <v>74</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>75</v>
@@ -6779,18 +6776,18 @@
         <v>74</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -6813,19 +6810,19 @@
         <v>109</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>278</v>
+        <v>81</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="P46" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q46" t="s" s="2">
         <v>74</v>
@@ -6874,7 +6871,7 @@
         <v>74</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>75</v>
@@ -6886,18 +6883,18 @@
         <v>74</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -6923,17 +6920,13 @@
         <v>81</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
       <c r="Q47" t="s" s="2">
         <v>74</v>
       </c>
@@ -6981,7 +6974,7 @@
         <v>74</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>75</v>
@@ -6993,18 +6986,18 @@
         <v>74</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7030,13 +7023,15 @@
         <v>81</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O48" s="2"/>
-      <c r="P48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="Q48" t="s" s="2">
         <v>74</v>
       </c>
@@ -7084,7 +7079,7 @@
         <v>74</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>75</v>
@@ -7096,29 +7091,29 @@
         <v>74</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
-        <v>74</v>
+        <v>296</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>74</v>
@@ -7130,18 +7125,16 @@
         <v>109</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>81</v>
+        <v>297</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>296</v>
-      </c>
+      <c r="P49" s="2"/>
       <c r="Q49" t="s" s="2">
         <v>74</v>
       </c>
@@ -7189,10 +7182,10 @@
         <v>74</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
@@ -7201,29 +7194,29 @@
         <v>74</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>298</v>
+        <v>74</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>74</v>
@@ -7235,15 +7228,17 @@
         <v>109</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P50" s="2"/>
       <c r="Q50" t="s" s="2">
         <v>74</v>
@@ -7292,10 +7287,10 @@
         <v>74</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
@@ -7304,29 +7299,29 @@
         <v>74</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
-        <v>74</v>
+        <v>306</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>74</v>
@@ -7338,18 +7333,20 @@
         <v>109</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="P51" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="Q51" t="s" s="2">
         <v>74</v>
       </c>
@@ -7397,7 +7394,7 @@
         <v>74</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>75</v>
@@ -7409,29 +7406,29 @@
         <v>74</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>308</v>
+        <v>74</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>74</v>
@@ -7440,23 +7437,19 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>309</v>
+        <v>81</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>310</v>
+        <v>93</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
       <c r="Q52" t="s" s="2">
         <v>74</v>
       </c>
@@ -7504,7 +7497,7 @@
         <v>74</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>307</v>
+        <v>95</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>75</v>
@@ -7516,29 +7509,29 @@
         <v>74</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -7550,15 +7543,17 @@
         <v>74</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="P53" s="2"/>
       <c r="Q53" t="s" s="2">
         <v>74</v>
@@ -7595,53 +7590,53 @@
         <v>74</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="AD53" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="AE53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>74</v>
@@ -7650,19 +7645,19 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>98</v>
+        <v>315</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>99</v>
+        <v>316</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>100</v>
+        <v>317</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>101</v>
+        <v>318</v>
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" t="s" s="2">
@@ -7700,42 +7695,42 @@
         <v>74</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="AD54" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="AE54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>105</v>
+        <v>319</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>74</v>
+        <v>320</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -7758,22 +7753,24 @@
         <v>109</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="P55" s="2"/>
       <c r="Q55" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="S55" t="s" s="2">
         <v>74</v>
       </c>
@@ -7817,7 +7814,7 @@
         <v>74</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>75</v>
@@ -7826,32 +7823,32 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>74</v>
+        <v>328</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>74</v>
@@ -7863,68 +7860,64 @@
         <v>109</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" s="2"/>
       <c r="Q56" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R56" t="s" s="2">
+      <c r="R56" s="2"/>
+      <c r="S56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG56" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>75</v>
@@ -7933,25 +7926,25 @@
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>322</v>
+        <v>74</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
-        <v>330</v>
+        <v>74</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" t="s" s="2">
@@ -7970,15 +7963,17 @@
         <v>109</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P57" s="2"/>
       <c r="Q57" t="s" s="2">
         <v>74</v>
@@ -8027,7 +8022,7 @@
         <v>74</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>75</v>
@@ -8039,18 +8034,18 @@
         <v>74</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8070,19 +8065,19 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P58" s="2"/>
       <c r="Q58" t="s" s="2">
@@ -8132,30 +8127,30 @@
         <v>74</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -8178,18 +8173,18 @@
         <v>74</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="P59" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="Q59" t="s" s="2">
         <v>74</v>
       </c>
@@ -8237,7 +8232,7 @@
         <v>74</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>75</v>
@@ -8249,18 +8244,18 @@
         <v>74</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8280,20 +8275,22 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="P60" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q60" t="s" s="2">
         <v>74</v>
@@ -8342,7 +8339,7 @@
         <v>74</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>75</v>
@@ -8354,18 +8351,18 @@
         <v>74</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8385,22 +8382,22 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="P61" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q61" t="s" s="2">
         <v>74</v>
@@ -8449,7 +8446,7 @@
         <v>74</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>75</v>
@@ -8461,18 +8458,18 @@
         <v>74</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -8495,19 +8492,19 @@
         <v>74</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="P62" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q62" t="s" s="2">
         <v>74</v>
@@ -8556,7 +8553,7 @@
         <v>74</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>75</v>
@@ -8568,18 +8565,18 @@
         <v>74</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -8602,19 +8599,17 @@
         <v>74</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>360</v>
+        <v>89</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q63" t="s" s="2">
         <v>74</v>
@@ -8663,7 +8658,7 @@
         <v>74</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>75</v>
@@ -8675,18 +8670,18 @@
         <v>74</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>160</v>
+        <v>367</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -8697,7 +8692,7 @@
         <v>75</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>74</v>
@@ -8709,18 +8704,16 @@
         <v>74</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>366</v>
+        <v>93</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>367</v>
+        <v>94</v>
       </c>
       <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>368</v>
-      </c>
+      <c r="P64" s="2"/>
       <c r="Q64" t="s" s="2">
         <v>74</v>
       </c>
@@ -8768,41 +8761,41 @@
         <v>74</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>365</v>
+        <v>95</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>369</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>74</v>
@@ -8814,15 +8807,17 @@
         <v>74</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="P65" s="2"/>
       <c r="Q65" t="s" s="2">
         <v>74</v>
@@ -8871,34 +8866,34 @@
         <v>74</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" t="s" s="2">
@@ -8911,24 +8906,26 @@
         <v>74</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>98</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="P66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="Q66" t="s" s="2">
         <v>74</v>
       </c>
@@ -8976,7 +8973,7 @@
         <v>74</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>75</v>
@@ -8993,17 +8990,17 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" t="s" s="2">
@@ -9016,26 +9013,24 @@
         <v>74</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>98</v>
+        <v>236</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>110</v>
+        <v>372</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>111</v>
+        <v>373</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
         <v>74</v>
       </c>
@@ -9059,13 +9054,13 @@
         <v>74</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>74</v>
+        <v>375</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>74</v>
+        <v>376</v>
       </c>
       <c r="AA67" t="s" s="2">
-        <v>74</v>
+        <v>377</v>
       </c>
       <c r="AB67" t="s" s="2">
         <v>74</v>
@@ -9083,7 +9078,7 @@
         <v>74</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>113</v>
+        <v>371</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>75</v>
@@ -9095,18 +9090,18 @@
         <v>74</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9129,18 +9124,20 @@
         <v>74</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>238</v>
+        <v>352</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="P68" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="Q68" t="s" s="2">
         <v>74</v>
       </c>
@@ -9164,31 +9161,31 @@
         <v>74</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>377</v>
+        <v>74</v>
       </c>
       <c r="Z68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG68" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>75</v>
@@ -9200,18 +9197,18 @@
         <v>74</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9234,19 +9231,19 @@
         <v>74</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="P69" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="Q69" t="s" s="2">
         <v>74</v>
@@ -9295,7 +9292,7 @@
         <v>74</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>75</v>
@@ -9307,18 +9304,18 @@
         <v>74</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9329,7 +9326,7 @@
         <v>75</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>74</v>
@@ -9341,19 +9338,19 @@
         <v>74</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="P70" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="Q70" t="s" s="2">
         <v>74</v>
@@ -9402,30 +9399,30 @@
         <v>74</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>74</v>
+        <v>395</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -9448,19 +9445,17 @@
         <v>74</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>392</v>
+        <v>89</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q71" t="s" s="2">
         <v>74</v>
@@ -9509,7 +9504,7 @@
         <v>74</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>75</v>
@@ -9518,21 +9513,21 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9555,18 +9550,16 @@
         <v>74</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>399</v>
+        <v>93</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>400</v>
+        <v>94</v>
       </c>
       <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>401</v>
-      </c>
+      <c r="P72" s="2"/>
       <c r="Q72" t="s" s="2">
         <v>74</v>
       </c>
@@ -9614,7 +9607,7 @@
         <v>74</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>398</v>
+        <v>95</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>75</v>
@@ -9623,32 +9616,32 @@
         <v>80</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>397</v>
+        <v>74</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>74</v>
@@ -9660,15 +9653,17 @@
         <v>74</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="P73" s="2"/>
       <c r="Q73" t="s" s="2">
         <v>74</v>
@@ -9717,34 +9712,34 @@
         <v>74</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" t="s" s="2">
@@ -9757,24 +9752,26 @@
         <v>74</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>98</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="P74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="Q74" t="s" s="2">
         <v>74</v>
       </c>
@@ -9822,7 +9819,7 @@
         <v>74</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>75</v>
@@ -9839,48 +9836,46 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>110</v>
+        <v>404</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>101</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
-        <v>112</v>
+        <v>406</v>
       </c>
       <c r="Q75" t="s" s="2">
         <v>74</v>
@@ -9905,13 +9900,13 @@
         <v>74</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>74</v>
+        <v>407</v>
       </c>
       <c r="AA75" t="s" s="2">
-        <v>74</v>
+        <v>408</v>
       </c>
       <c r="AB75" t="s" s="2">
         <v>74</v>
@@ -9929,30 +9924,30 @@
         <v>74</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>113</v>
+        <v>403</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -9963,7 +9958,7 @@
         <v>75</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>74</v>
@@ -9975,17 +9970,17 @@
         <v>74</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>117</v>
+        <v>410</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>406</v>
+        <v>200</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="Q76" t="s" s="2">
         <v>74</v>
@@ -10010,54 +10005,54 @@
         <v>74</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="Z76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG76" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AA76" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>405</v>
-      </c>
       <c r="AH76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -10080,17 +10075,19 @@
         <v>74</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="P77" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="Q77" t="s" s="2">
         <v>74</v>
@@ -10139,7 +10136,7 @@
         <v>74</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>75</v>
@@ -10151,12 +10148,12 @@
         <v>74</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>415</v>
@@ -10173,7 +10170,7 @@
         <v>75</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>74</v>
@@ -10185,19 +10182,19 @@
         <v>74</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>86</v>
+        <v>236</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>205</v>
+        <v>416</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>207</v>
+        <v>418</v>
       </c>
       <c r="P78" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="Q78" t="s" s="2">
         <v>74</v>
@@ -10222,13 +10219,13 @@
         <v>74</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>74</v>
+        <v>375</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>74</v>
+        <v>420</v>
       </c>
       <c r="AA78" t="s" s="2">
-        <v>74</v>
+        <v>421</v>
       </c>
       <c r="AB78" t="s" s="2">
         <v>74</v>
@@ -10252,24 +10249,24 @@
         <v>75</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10280,7 +10277,7 @@
         <v>75</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>74</v>
@@ -10292,20 +10289,18 @@
         <v>74</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="P79" s="2"/>
       <c r="Q79" t="s" s="2">
         <v>74</v>
       </c>
@@ -10329,54 +10324,54 @@
         <v>74</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="Z79" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG79" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AA79" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>417</v>
-      </c>
       <c r="AH79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -10399,16 +10394,16 @@
         <v>74</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>238</v>
+        <v>429</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="P80" s="2"/>
       <c r="Q80" t="s" s="2">
@@ -10434,31 +10429,31 @@
         <v>74</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>377</v>
+        <v>74</v>
       </c>
       <c r="Z80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG80" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>75</v>
@@ -10470,18 +10465,18 @@
         <v>74</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10504,18 +10499,18 @@
         <v>74</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>431</v>
+        <v>358</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="P81" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="Q81" t="s" s="2">
         <v>74</v>
       </c>
@@ -10563,7 +10558,7 @@
         <v>74</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>75</v>
@@ -10575,18 +10570,18 @@
         <v>74</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -10594,32 +10589,34 @@
       </c>
       <c r="F82" s="2"/>
       <c r="G82" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>360</v>
+        <v>117</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="P82" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="Q82" t="s" s="2">
         <v>74</v>
@@ -10644,13 +10641,13 @@
         <v>74</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>74</v>
+        <v>442</v>
       </c>
       <c r="AA82" t="s" s="2">
-        <v>74</v>
+        <v>443</v>
       </c>
       <c r="AB82" t="s" s="2">
         <v>74</v>
@@ -10668,30 +10665,30 @@
         <v>74</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -10699,7 +10696,7 @@
       </c>
       <c r="F83" s="2"/>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>80</v>
@@ -10708,26 +10705,24 @@
         <v>74</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>117</v>
+        <v>236</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="P83" s="2"/>
       <c r="Q83" t="s" s="2">
         <v>74</v>
       </c>
@@ -10751,34 +10746,34 @@
         <v>74</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="Z83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG83" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AA83" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="AH83" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>80</v>
@@ -10787,18 +10782,18 @@
         <v>74</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -10815,72 +10810,76 @@
         <v>74</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>74</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N84" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="Q84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R84" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG84" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="P84" s="2"/>
-      <c r="Q84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R84" s="2"/>
-      <c r="S84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>75</v>
@@ -10892,18 +10891,18 @@
         <v>74</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -10920,76 +10919,72 @@
         <v>74</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>278</v>
+        <v>455</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="Q85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R85" s="2"/>
+      <c r="S85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG85" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="Q85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R85" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>75</v>
@@ -11001,18 +10996,18 @@
         <v>74</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11035,17 +11030,19 @@
         <v>74</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P86" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="Q86" t="s" s="2">
         <v>74</v>
@@ -11094,7 +11091,7 @@
         <v>74</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>75</v>
@@ -11106,18 +11103,18 @@
         <v>74</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -11128,7 +11125,7 @@
         <v>75</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>74</v>
@@ -11140,19 +11137,19 @@
         <v>74</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="N87" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="P87" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="P87" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="Q87" t="s" s="2">
         <v>74</v>
@@ -11201,30 +11198,30 @@
         <v>74</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -11235,7 +11232,7 @@
         <v>75</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>74</v>
@@ -11247,20 +11244,16 @@
         <v>74</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" s="2"/>
       <c r="Q88" t="s" s="2">
         <v>74</v>
       </c>
@@ -11284,13 +11277,13 @@
         <v>74</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>74</v>
+        <v>375</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>74</v>
+        <v>474</v>
       </c>
       <c r="AA88" t="s" s="2">
-        <v>74</v>
+        <v>475</v>
       </c>
       <c r="AB88" t="s" s="2">
         <v>74</v>
@@ -11308,34 +11301,34 @@
         <v>74</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
-        <v>74</v>
+        <v>477</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" t="s" s="2">
@@ -11354,16 +11347,18 @@
         <v>74</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="O89" s="2"/>
-      <c r="P89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="Q89" t="s" s="2">
         <v>74</v>
       </c>
@@ -11387,31 +11382,31 @@
         <v>74</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>377</v>
+        <v>74</v>
       </c>
       <c r="Z89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG89" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>75</v>
@@ -11423,22 +11418,22 @@
         <v>74</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
-        <v>479</v>
+        <v>74</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" t="s" s="2">
@@ -11457,18 +11452,16 @@
         <v>74</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="O90" s="2"/>
-      <c r="P90" t="s" s="2">
-        <v>483</v>
-      </c>
+      <c r="P90" s="2"/>
       <c r="Q90" t="s" s="2">
         <v>74</v>
       </c>
@@ -11516,7 +11509,7 @@
         <v>74</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>75</v>
@@ -11528,18 +11521,18 @@
         <v>74</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11562,13 +11555,13 @@
         <v>74</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>480</v>
+        <v>81</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
@@ -11619,7 +11612,7 @@
         <v>74</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>75</v>
@@ -11631,18 +11624,18 @@
         <v>74</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -11653,7 +11646,7 @@
         <v>75</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>74</v>
@@ -11665,16 +11658,18 @@
         <v>74</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>81</v>
+        <v>384</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O92" s="2"/>
-      <c r="P92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="Q92" t="s" s="2">
         <v>74</v>
       </c>
@@ -11722,124 +11717,19 @@
         <v>74</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="D93" s="2"/>
-      <c r="E93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="F93" s="2"/>
-      <c r="G93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="Q93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R93" s="2"/>
-      <c r="S93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
